--- a/artfynd/A 61850-2021 artfynd.xlsx
+++ b/artfynd/A 61850-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61850-2021 artfynd.xlsx
+++ b/artfynd/A 61850-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62023171</v>
+        <v>62023170</v>
       </c>
       <c r="B2" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>1204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626215.6478240907</v>
+        <v>626265</v>
       </c>
       <c r="R2" t="n">
-        <v>7150994.339679484</v>
+        <v>7150939</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2016-09-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-09-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,6 +777,325 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>16746374</v>
+      </c>
+      <c r="B3" t="n">
+        <v>90932</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Tallsjöbergen: Lappvägamyran, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>625939</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7151273</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2014-09-25</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2014-09-25</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>låga # tall</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>16746373</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91962</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tallsjöbergen: Lappvägamyran, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>625923</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7151260</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2014-09-25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2014-09-25</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>låga # tall</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>62023171</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hundbergsmon, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>626216</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7150994</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2016-09-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2016-09-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg, Sven Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61850-2021 artfynd.xlsx
+++ b/artfynd/A 61850-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62023170</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16746374</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,6 +1006,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16746373</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,8 +1116,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62023171</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>